--- a/data/trans_orig/IP07A20-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A20-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2007 (tasa de respuesta: 99,0%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2007 (tasa de respuesta: 99,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24810</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37423</t>
+          <t>37256</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23009</t>
+          <t>22237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36884</t>
+          <t>36126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50135</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69704</t>
+          <t>69242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18861</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31614</t>
+          <t>31734</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>41681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49376</t>
+          <t>49217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68873</t>
+          <t>68534</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13208</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>25496</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35611</t>
+          <t>36328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50954</t>
+          <t>51566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26607</t>
+          <t>27264</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41054</t>
+          <t>41177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65749</t>
+          <t>67152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88469</t>
+          <t>88274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39721</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55757</t>
+          <t>55487</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44211</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60171</t>
+          <t>59479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89281</t>
+          <t>88864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112825</t>
+          <t>110775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,33%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14479</t>
+          <t>14248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,47 +1690,47 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>18764</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>12309</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>25298</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>6,04%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>15,86%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>18764</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>12776</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>26423</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27305</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39227</t>
+          <t>39452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24855</t>
+          <t>24442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37450</t>
+          <t>37833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55966</t>
+          <t>55567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>72791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29101</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,49 +2224,49 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>48,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>24580</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>18940</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>31928</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>37,08%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>28,57%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>48,16%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>24580</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>18422</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>30755</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,08%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>27,79%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>46,39%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>78</t>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>39765</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57164</t>
+          <t>56784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13694</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>18134</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28789</t>
+          <t>28800</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44146</t>
+          <t>44472</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25236</t>
+          <t>25437</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40072</t>
+          <t>40548</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58405</t>
+          <t>57801</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80616</t>
+          <t>79232</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34800</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50631</t>
+          <t>49568</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42677</t>
+          <t>42720</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>58713</t>
+          <t>58492</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>80436</t>
+          <t>82223</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103657</t>
+          <t>103921</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>15947</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16337</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>130357</t>
+          <t>128755</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>157741</t>
+          <t>158587</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>112237</t>
+          <t>113696</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>141656</t>
+          <t>142355</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>250338</t>
+          <t>248371</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>292281</t>
+          <t>290182</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,82%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124910</t>
+          <t>125097</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>152441</t>
+          <t>154385</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>145249</t>
+          <t>146029</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175793</t>
+          <t>175146</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>278823</t>
+          <t>280819</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>320449</t>
+          <t>320318</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19229</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34758</t>
+          <t>35781</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>55043</t>
+          <t>55196</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>59229</t>
+          <t>60014</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>84981</t>
+          <t>85292</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23038</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,39 +3927,39 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>4175</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>4162</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33625</t>
+          <t>34658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>48286</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>37188</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51640</t>
+          <t>51271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75732</t>
+          <t>75429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94511</t>
+          <t>94769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,53%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14525</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27611</t>
+          <t>26835</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18387</t>
+          <t>18431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32084</t>
+          <t>32201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36806</t>
+          <t>37158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54261</t>
+          <t>55542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52310</t>
+          <t>52391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67884</t>
+          <t>67006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43447</t>
+          <t>44602</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59492</t>
+          <t>60091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101357</t>
+          <t>101340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123392</t>
+          <t>123694</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,44%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24951</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39229</t>
+          <t>38926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28229</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43611</t>
+          <t>42887</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55730</t>
+          <t>57207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76598</t>
+          <t>77894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33768</t>
+          <t>33528</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46563</t>
+          <t>46333</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33904</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47506</t>
+          <t>47477</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72225</t>
+          <t>72589</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90404</t>
+          <t>90748</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,7%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>26511</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28239</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>33831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50540</t>
+          <t>51255</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>12483</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40401</t>
+          <t>40857</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56564</t>
+          <t>57049</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>45693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61244</t>
+          <t>61796</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90965</t>
+          <t>88841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113920</t>
+          <t>112435</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26410</t>
+          <t>26118</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42606</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20843</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34903</t>
+          <t>35131</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50878</t>
+          <t>50877</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72489</t>
+          <t>72398</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>12793</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14208</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22299</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>175024</t>
+          <t>174466</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>203519</t>
+          <t>204506</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>176634</t>
+          <t>177438</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>205886</t>
+          <t>206376</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>358713</t>
+          <t>362196</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>402789</t>
+          <t>401932</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>92578</t>
+          <t>92885</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121803</t>
+          <t>122301</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>95099</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124089</t>
+          <t>124125</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>196080</t>
+          <t>196475</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>236945</t>
+          <t>233712</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>28313</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30149</t>
+          <t>30710</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>51591</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29045</t>
+          <t>29864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43356</t>
+          <t>43908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25933</t>
+          <t>25781</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40498</t>
+          <t>40360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59970</t>
+          <t>59672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80822</t>
+          <t>80571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>19885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>33936</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23428</t>
+          <t>24080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38451</t>
+          <t>38835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47531</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67788</t>
+          <t>68135</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18772</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46231</t>
+          <t>46325</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63353</t>
+          <t>63585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44939</t>
+          <t>45628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61566</t>
+          <t>62563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96278</t>
+          <t>96751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119555</t>
+          <t>119215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,98%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>29110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45880</t>
+          <t>44597</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34900</t>
+          <t>34228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51651</t>
+          <t>51022</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68745</t>
+          <t>68805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91065</t>
+          <t>90779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19104</t>
+          <t>18737</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27509</t>
+          <t>27756</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32474</t>
+          <t>32663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46357</t>
+          <t>45990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40970</t>
+          <t>41958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55505</t>
+          <t>55427</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78860</t>
+          <t>78691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97859</t>
+          <t>97638</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19366</t>
+          <t>19974</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33209</t>
+          <t>33581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14868</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38489</t>
+          <t>38649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56577</t>
+          <t>57079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13463</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47560</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65141</t>
+          <t>65562</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45770</t>
+          <t>45505</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62327</t>
+          <t>62085</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99104</t>
+          <t>98518</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122469</t>
+          <t>124708</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>59,66%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35843</t>
+          <t>35677</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53358</t>
+          <t>53407</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27952</t>
+          <t>27910</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43845</t>
+          <t>44211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67783</t>
+          <t>66335</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>90971</t>
+          <t>91621</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>23019</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>586</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>172509</t>
+          <t>172687</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>205403</t>
+          <t>204699</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>173476</t>
+          <t>173853</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>203966</t>
+          <t>204992</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>356455</t>
+          <t>354578</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>400078</t>
+          <t>402416</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>118373</t>
+          <t>116979</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>148833</t>
+          <t>148668</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>116070</t>
+          <t>116458</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>147393</t>
+          <t>146823</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>243987</t>
+          <t>244320</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>286054</t>
+          <t>288686</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23636</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40761</t>
+          <t>39371</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40641</t>
+          <t>38879</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49672</t>
+          <t>49835</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>74192</t>
+          <t>72745</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
